--- a/output/pdf_financials_xlsx/VERS.xlsx
+++ b/output/pdf_financials_xlsx/VERS.xlsx
@@ -1095,10 +1095,10 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>4.397281</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.892727</v>
       </c>
     </row>
     <row r="35">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>4.397281</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.892727</v>
       </c>
     </row>
     <row r="37">
@@ -1417,10 +1417,10 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>8.000874</v>
+        <v>3.603593</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>4.378231</v>
+        <v>3.485504</v>
       </c>
     </row>
     <row r="49">
@@ -3046,13 +3046,13 @@
         <v>0</v>
       </c>
       <c r="C124" s="3" t="n">
-        <v>0</v>
+        <v>-0.065709</v>
       </c>
       <c r="D124" s="3" t="n">
-        <v>0</v>
+        <v>-0.131776</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>0</v>
+        <v>-0.113978</v>
       </c>
     </row>
     <row r="125">
@@ -3065,13 +3065,13 @@
         <v>0</v>
       </c>
       <c r="C125" s="3" t="n">
-        <v>0</v>
+        <v>-0.065709</v>
       </c>
       <c r="D125" s="3" t="n">
-        <v>0</v>
+        <v>-0.131776</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>0</v>
+        <v>-0.113978</v>
       </c>
     </row>
     <row r="126">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5426,7 +5426,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -6970,7 +6974,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">

--- a/output/pdf_financials_xlsx/VERS.xlsx
+++ b/output/pdf_financials_xlsx/VERS.xlsx
@@ -1084,15 +1084,11 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>6.369903</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>7.962977</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>4.397281</v>
@@ -1107,15 +1103,11 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>0</v>
@@ -1130,15 +1122,11 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>6.369903</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>7.962977</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>4.397281</v>
@@ -1153,15 +1141,11 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0.461699</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>0.035</v>
@@ -1176,15 +1160,11 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>0</v>
@@ -1199,15 +1179,11 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>0</v>
@@ -1222,15 +1198,11 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>0</v>
@@ -1245,15 +1217,11 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0.461699</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>0.035</v>
@@ -1268,15 +1236,11 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>0</v>
@@ -1291,15 +1255,11 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>0</v>
@@ -1314,15 +1274,11 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>0</v>
@@ -1337,15 +1293,11 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0</v>
@@ -1360,15 +1312,11 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0</v>
@@ -1383,15 +1331,11 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0</v>
@@ -1406,15 +1350,11 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>1.877257</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>2.855449</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>3.603593</v>
@@ -1429,15 +1369,11 @@
           <t xml:space="preserve">  Total Current Assets</t>
         </is>
       </c>
-      <c r="B49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C49" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B49" s="3" t="n">
+        <v>8.39016</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>11.280125</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>8.035874</v>
@@ -1452,15 +1388,11 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0</v>
@@ -1475,15 +1407,11 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>0</v>
@@ -1498,15 +1426,11 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>0</v>
@@ -1521,15 +1445,11 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0.231907</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0.295176</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0.23484</v>
@@ -1544,15 +1464,11 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>0</v>
@@ -1594,15 +1510,11 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0</v>
@@ -1617,15 +1529,11 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0</v>
@@ -1640,15 +1548,11 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0.220067</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0.162658</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0.109011</v>
@@ -1663,15 +1567,11 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>0</v>
@@ -1686,15 +1586,11 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>0</v>
@@ -1709,15 +1605,11 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0.418161</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0.715127</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0.495862</v>
@@ -1732,15 +1624,11 @@
           <t xml:space="preserve">  Total Long-Term Assets</t>
         </is>
       </c>
-      <c r="B62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C62" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B62" s="3" t="n">
+        <v>0.638228</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>0.877785</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>0.604873</v>
@@ -1755,15 +1643,11 @@
           <t>Total Assets</t>
         </is>
       </c>
-      <c r="B63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C63" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B63" s="3" t="n">
+        <v>9.028388</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>12.15791</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>8.640746999999999</v>
@@ -1778,21 +1662,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>0</v>
+        <v>1.175409</v>
       </c>
       <c r="E64" s="3" t="n">
-        <v>0</v>
+        <v>2.782502</v>
       </c>
     </row>
     <row r="65">
@@ -1801,15 +1681,11 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>0</v>
@@ -1824,15 +1700,11 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0.186254</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0.419951</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>0.866688</v>
@@ -1847,21 +1719,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.07389</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.0825</v>
       </c>
     </row>
     <row r="68">
@@ -1870,15 +1738,11 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.619962</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1.152722</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>1.249299</v>
@@ -1893,15 +1757,11 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0.145743</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0.144537</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>0.143331</v>
@@ -1916,15 +1776,11 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>0</v>
@@ -1939,15 +1795,11 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0.145743</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0.144537</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>0.143331</v>
@@ -1962,15 +1814,11 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0.292</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>0.065</v>
@@ -1985,15 +1833,11 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>0</v>
@@ -2008,15 +1852,11 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0.292</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>0.065</v>
@@ -2031,15 +1871,11 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>1.043872</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>1.010139</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>6.198413</v>
@@ -2054,15 +1890,11 @@
           <t xml:space="preserve">  Total Current Liabilities</t>
         </is>
       </c>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B76" s="3" t="n">
+        <v>2.061577</v>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>2.599398</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>7.656043</v>
@@ -2077,15 +1909,11 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>0</v>
@@ -2100,15 +1928,11 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>0</v>
@@ -2123,15 +1947,11 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>0</v>
@@ -2146,15 +1966,11 @@
           <t>Debt-to-Equity</t>
         </is>
       </c>
-      <c r="B80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B80" s="3" t="n">
+        <v>0.0217010607154115</v>
+      </c>
+      <c r="C80" s="3" t="n">
+        <v>0.01540987997017326</v>
       </c>
       <c r="D80" s="3" t="n">
         <v>0.1703536956855045</v>
@@ -2169,15 +1985,11 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D81" s="3" t="n">
         <v>0</v>
@@ -2192,15 +2004,11 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D82" s="3" t="n">
         <v>0</v>
@@ -2215,15 +2023,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D83" s="3" t="n">
         <v>0</v>
@@ -2238,15 +2042,11 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D84" s="3" t="n">
         <v>0</v>
@@ -2261,15 +2061,11 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0.250872</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0.17901</v>
       </c>
       <c r="D85" s="3" t="n">
         <v>0.143331</v>
@@ -2284,15 +2080,11 @@
           <t xml:space="preserve">  Total Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C86" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B86" s="3" t="n">
+        <v>0.250872</v>
+      </c>
+      <c r="C86" s="3" t="n">
+        <v>0.17901</v>
       </c>
       <c r="D86" s="3" t="n">
         <v>0.143331</v>
@@ -2307,15 +2099,11 @@
           <t>Total Liabilities</t>
         </is>
       </c>
-      <c r="B87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C87" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B87" s="3" t="n">
+        <v>2.312449</v>
+      </c>
+      <c r="C87" s="3" t="n">
+        <v>2.778408</v>
       </c>
       <c r="D87" s="3" t="n">
         <v>7.799374</v>
@@ -2330,15 +2118,11 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>20.384147</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>30.132345</v>
       </c>
       <c r="D88" s="3" t="n">
         <v>30.264179</v>
@@ -2353,15 +2137,11 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D89" s="3" t="n">
         <v>0</v>
@@ -2376,15 +2156,11 @@
           <t xml:space="preserve">  Retained Earnings</t>
         </is>
       </c>
-      <c r="B90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C90" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B90" s="3" t="n">
+        <v>-15.017804</v>
+      </c>
+      <c r="C90" s="3" t="n">
+        <v>-24.555394</v>
       </c>
       <c r="D90" s="3" t="n">
         <v>-34.476242</v>
@@ -2399,15 +2175,11 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>-0.234186</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>-0.745243</v>
       </c>
       <c r="D91" s="3" t="n">
         <v>-0.636527</v>
@@ -2422,15 +2194,11 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>1.583782</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>4.547794</v>
       </c>
       <c r="D92" s="3" t="n">
         <v>5.606507</v>
@@ -2445,15 +2213,11 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D93" s="3" t="n">
         <v>0</v>
@@ -2468,15 +2232,11 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>6.715939</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>9.379502</v>
       </c>
       <c r="D94" s="3" t="n">
         <v>0.841373</v>
@@ -2491,15 +2251,11 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D95" s="3" t="n">
         <v>0</v>
@@ -2514,15 +2270,11 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>6.715939</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>9.379502</v>
       </c>
       <c r="D96" s="3" t="n">
         <v>0.841373</v>
@@ -2537,15 +2289,11 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.7438691159484949</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.7714732219600243</v>
       </c>
       <c r="D97" s="3" t="n">
         <v>0.09737271557655837</v>
@@ -2783,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.126714</v>
       </c>
       <c r="E110" s="3" t="n">
-        <v>0</v>
+        <v>0.552359</v>
       </c>
     </row>
     <row r="111">
@@ -3283,7 +3031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H167"/>
+  <dimension ref="A1:H178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3355,15 +3103,11 @@
           <t>CashAndCashEquivalents</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E2" s="5" t="n">
+        <v>6.369903</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>7.962977</v>
       </c>
       <c r="G2" s="5" t="n">
         <v>4.397281</v>
@@ -3393,15 +3137,11 @@
           <t>AccountsReceivable</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E3" s="5" t="n">
+        <v>0.143</v>
+      </c>
+      <c r="F3" s="5" t="n">
+        <v>0.461699</v>
       </c>
       <c r="G3" s="5" t="n">
         <v>0.035</v>
@@ -3431,15 +3171,11 @@
           <t>OtherPayable</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E4" s="5" t="n">
+        <v>0.186254</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.419951</v>
       </c>
       <c r="G4" s="5" t="n">
         <v>0.605666</v>
@@ -3505,15 +3241,11 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E6" s="5" t="n">
+        <v>1.402035</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>1.733259</v>
       </c>
       <c r="G6" s="5" t="n">
         <v>1.350435</v>
@@ -3543,15 +3275,11 @@
           <t>TaxesReceivable</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E7" s="5" t="n">
+        <v>0.026553</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.114094</v>
       </c>
       <c r="G7" s="5" t="n">
         <v>0.204815</v>
@@ -3619,15 +3347,11 @@
           <t>CurrentAssets</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E9" s="5" t="n">
+        <v>8.39016</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>11.280125</v>
       </c>
       <c r="G9" s="5" t="n">
         <v>8.035874</v>
@@ -3773,15 +3497,11 @@
           <t>TotalAssets</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E13" s="5" t="n">
+        <v>9.028388</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>12.15791</v>
       </c>
       <c r="G13" s="5" t="n">
         <v>8.640746999999999</v>
@@ -3811,15 +3531,11 @@
           <t>PayablesAndAccruedExpenses</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E14" s="5" t="n">
+        <v>0.619962</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>1.152722</v>
       </c>
       <c r="G14" s="5" t="n">
         <v>1.249299</v>
@@ -3849,15 +3565,11 @@
           <t>CurrentDeferredRevenue</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E15" s="5" t="n">
+        <v>0.252</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>0.292</v>
       </c>
       <c r="G15" s="5" t="n">
         <v>0.065</v>
@@ -4063,15 +3775,11 @@
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E21" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>1.025</v>
       </c>
       <c r="G21" s="5" t="n">
         <v>1.025</v>
@@ -4103,15 +3811,11 @@
           <t>CurrentDebt</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E22" s="5" t="n">
+        <v>0.145743</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>0.144537</v>
       </c>
       <c r="G22" s="5" t="n">
         <v>0.143331</v>
@@ -4141,15 +3845,11 @@
           <t>TotalLiabilities</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E23" s="5" t="n">
+        <v>2.312449</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>2.778408</v>
       </c>
       <c r="G23" s="5" t="n">
         <v>7.799374</v>
@@ -4179,15 +3879,11 @@
           <t>CapitalStock</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E24" s="5" t="n">
+        <v>20.384147</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>30.132345</v>
       </c>
       <c r="G24" s="5" t="n">
         <v>30.264179</v>
@@ -4291,15 +3987,11 @@
           <t>GainsLossesNotAffectingRetainedEarnings</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E27" s="5" t="n">
+        <v>-0.234186</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-0.745243</v>
       </c>
       <c r="G27" s="5" t="n">
         <v>-0.636527</v>
@@ -4329,15 +4021,11 @@
           <t>RetainedEarnings</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E28" s="5" t="n">
+        <v>-15.017804</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-24.555394</v>
       </c>
       <c r="G28" s="5" t="n">
         <v>-34.476242</v>
@@ -4459,104 +4147,110 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Net loss for the year $</t>
+          <t>Restricted cash 3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>-19.458438</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>-46.607285</v>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>0.094088</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.013592</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Prepaid expenses 14</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>0.354581</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.11621</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.23613</v>
-      </c>
-      <c r="H33" s="5" t="n">
-        <v>0.261747</v>
+        <v>0.9945040000000001</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SAFE issued for advisory services</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Equipment 15</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.231907</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.025</v>
+        <v>0.295176</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4567,60 +4261,60 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Provision for legal settlement</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Right-of-use asset 16</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>0.220067</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.162658</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H35" s="5" t="n">
-        <v>6.307258</v>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Foreign exchange effect on convertible debenture</t>
+          <t>Deferred grant 3</t>
         </is>
       </c>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E36" s="5" t="n">
+        <v>0.074321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4632,143 +4326,149 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H36" s="5" t="n">
-        <v>0.154109</v>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Interest and accretion expense</t>
+          <t>Lease liability - ST 17</t>
         </is>
       </c>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.126714</v>
-      </c>
-      <c r="H37" s="5" t="n">
-        <v>0.552359</v>
+      <c r="E37" s="5" t="n">
+        <v>0.115294</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.129676</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>CURRENT</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Issuance of advisory units and warrants for services</t>
+          <t>Lease liability - LT 17</t>
         </is>
       </c>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.371507</v>
-      </c>
-      <c r="H38" s="5" t="n">
-        <v>0.061049</v>
+      <c r="E38" s="5" t="n">
+        <v>0.105129</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>0.034473</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Share based payments</t>
+          <t>Contributed surplus 13</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>1.583782</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>1.5549</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>2.706068</v>
-      </c>
-      <c r="H39" s="5" t="n">
-        <v>7.850119</v>
+        <v>4.547794</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Write off of equipment</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.024128</v>
+          <t>Total Shareholders' Equity</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>6.715939</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>9.379502</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4779,65 +4479,73 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>SHAREHOLDERS' EQUITY</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Items not involving cash total</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
+          <t>Total Liabilities and Shareholders' Equity $</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TotalLiabilitiesAndTotalEquityGrossMinorityInterest</t>
+        </is>
+      </c>
       <c r="E41" s="5" t="n">
-        <v>0.203595</v>
+        <v>9.028388</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>-7.457868</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>-15.968891</v>
-      </c>
-      <c r="H41" s="5" t="n">
-        <v>-31.420644</v>
+        <v>12.15791</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>cash_flow</t>
+          <t>balance_sheet</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Subsequent event</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Accounts receivable</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ChangeInReceivables</t>
-        </is>
-      </c>
+          <t>Approved and authorized for issue on behalf of the Board on November</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" s="5" t="n">
-        <v>-0.111637</v>
+        <v>0.002022</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>-0.318699</v>
-      </c>
-      <c r="G42" s="5" t="n">
-        <v>0.108</v>
-      </c>
-      <c r="H42" s="5" t="n">
-        <v>-0.065</v>
+        <v>1.4e-05</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="43">
@@ -4848,26 +4556,34 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Contract assets and unbilled revenue</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" s="5" t="n">
-        <v>-0.612199</v>
-      </c>
-      <c r="F43" s="5" t="n">
-        <v>-0.331224</v>
+          <t>Net loss for the year $</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0516</v>
+        <v>-19.458438</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.098359</v>
+        <v>-46.607285</v>
       </c>
     </row>
     <row r="44">
@@ -4878,26 +4594,32 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Tax receivable</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" s="5" t="n">
-        <v>0.011608</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-0.08754099999999999</v>
+        <v>0.11621</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.178262</v>
+        <v>0.23613</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>-0.170149</v>
+        <v>0.261747</v>
       </c>
     </row>
     <row r="45">
@@ -4908,30 +4630,30 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="n">
-        <v>-0.045943</v>
+          <t>SAFE issued for advisory services</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-0.639923</v>
+        <v>0.025</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-1.088096</v>
-      </c>
-      <c r="H45" s="5" t="n">
-        <v>0.648326</v>
+        <v>0.025</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -4942,12 +4664,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Deferred financing costs</t>
+          <t>Provision for legal settlement</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4967,7 +4689,7 @@
         </is>
       </c>
       <c r="H46" s="5" t="n">
-        <v>-0.080993</v>
+        <v>6.307258</v>
       </c>
     </row>
     <row r="47">
@@ -4978,30 +4700,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Accounts payable and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>-0.370471</v>
-      </c>
-      <c r="F47" s="5" t="n">
-        <v>0.53276</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.629337</v>
+          <t>Foreign exchange effect on convertible debenture</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H47" s="5" t="n">
-        <v>1.615703</v>
+        <v>0.154109</v>
       </c>
     </row>
     <row r="48">
@@ -5012,30 +4736,34 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Deferred revenue</t>
+          <t>Interest and accretion expense</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>ChangeInOtherWorkingCapital</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.152</v>
-      </c>
-      <c r="F48" s="5" t="n">
-        <v>0.04</v>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.187</v>
+        <v>0.126714</v>
       </c>
       <c r="H48" s="5" t="n">
-        <v>-0.065</v>
+        <v>0.552359</v>
       </c>
     </row>
     <row r="49">
@@ -5046,28 +4774,30 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Deferred grant</t>
+          <t>Issuance of advisory units and warrants for services</t>
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" s="5" t="n">
-        <v>-0.778596</v>
-      </c>
-      <c r="F49" s="5" t="n">
-        <v>-0.074321</v>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.074321</v>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.371507</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.061049</v>
       </c>
     </row>
     <row r="50">
@@ -5078,30 +4808,32 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Net cash used in operating activities</t>
+          <t>Share based payments</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>-1.551643</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F50" s="5" t="n">
-        <v>-8.570513</v>
+        <v>1.5549</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-16.707633</v>
+        <v>2.706068</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-29.439398</v>
+        <v>7.850119</v>
       </c>
     </row>
     <row r="51">
@@ -5112,12 +4844,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Due from related parties</t>
+          <t>Write off of equipment</t>
         </is>
       </c>
       <c r="D51" t="inlineStr"/>
@@ -5132,10 +4864,12 @@
         </is>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.680434</v>
-      </c>
-      <c r="H51" s="5" t="n">
-        <v>-1.070582</v>
+        <v>0.024128</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -5146,28 +4880,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Investment in equipment</t>
+          <t>Items not involving cash total</t>
         </is>
       </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E52" s="5" t="n">
+        <v>0.203595</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>-0.12207</v>
+        <v>-7.457868</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.148032</v>
+        <v>-15.968891</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-0.185155</v>
+        <v>-31.420644</v>
       </c>
     </row>
     <row r="53">
@@ -5178,34 +4910,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Net cash used in investing activities</t>
+          <t>Accounts receivable</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>-0.111637</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>-0.318699</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.828466</v>
+        <v>0.108</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-1.255737</v>
+        <v>-0.065</v>
       </c>
     </row>
     <row r="54">
@@ -5216,26 +4944,26 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Repayments of loans</t>
+          <t>Contract assets and unbilled revenue</t>
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" s="5" t="n">
-        <v>-0.614499</v>
+        <v>-0.612199</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>-0.003876</v>
+        <v>-0.331224</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.007752</v>
+        <v>0.0516</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-0.007752</v>
+        <v>0.098359</v>
       </c>
     </row>
     <row r="55">
@@ -5246,30 +4974,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of promissory notes and convertible debentures</t>
+          <t>Tax receivable</t>
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E55" s="5" t="n">
+        <v>0.011608</v>
+      </c>
+      <c r="F55" s="5" t="n">
+        <v>-0.08754099999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>5.54533</v>
+        <v>-0.178262</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>2</v>
+        <v>-0.170149</v>
       </c>
     </row>
     <row r="56">
@@ -5280,30 +5004,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of equity instruments</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaid expenses</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="n">
+        <v>-0.045943</v>
+      </c>
+      <c r="F56" s="5" t="n">
+        <v>-0.639923</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>11.691257</v>
+        <v>-1.088096</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>9.839456999999999</v>
+        <v>0.648326</v>
       </c>
     </row>
     <row r="57">
@@ -5314,12 +5038,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Proceeds from obligation to issue shares</t>
+          <t>Deferred financing costs</t>
         </is>
       </c>
       <c r="D57" t="inlineStr"/>
@@ -5333,13 +5057,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G57" s="5" t="n">
-        <v>0.083456</v>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-0.080993</v>
       </c>
     </row>
     <row r="58">
@@ -5350,32 +5074,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Proceeds from issuance of units</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Accounts payable and accrued liabilities</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-0.370471</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>0.53276</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.629337</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>17.518269</v>
+        <v>1.615703</v>
       </c>
     </row>
     <row r="59">
@@ -5386,28 +5108,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Private placement issuance costs</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred revenue</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>ChangeInOtherWorkingCapital</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>0.152</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>-0.77918</v>
+        <v>0.04</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-1.308785</v>
+        <v>-0.187</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>-1.697576</v>
+        <v>-0.065</v>
       </c>
     </row>
     <row r="60">
@@ -5418,32 +5142,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Lease payments</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>RepaymentOfDebt</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Deferred grant</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" s="5" t="n">
+        <v>-0.778596</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.065709</v>
+        <v>-0.074321</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.131776</v>
-      </c>
-      <c r="H60" s="5" t="n">
-        <v>-0.113978</v>
+        <v>-0.074321</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="61">
@@ -5454,30 +5174,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Net cash provided by financing activities</t>
+          <t>Net cash used in operating activities</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FinancingCashFlow</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>0.440501</v>
+        <v>-1.551643</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>10.716218</v>
+        <v>-8.570513</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>15.87173</v>
+        <v>-16.707633</v>
       </c>
       <c r="H61" s="5" t="n">
-        <v>27.53842</v>
+        <v>-29.439398</v>
       </c>
     </row>
     <row r="62">
@@ -5488,30 +5208,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Foreign exchange effect on cash</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>EffectOfExchangeRateChanges</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="n">
-        <v>-0.010386</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>-0.511057</v>
+          <t>Due from related parties</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.402341</v>
+        <v>-0.680434</v>
       </c>
       <c r="H62" s="5" t="n">
-        <v>-0.347839</v>
+        <v>-1.070582</v>
       </c>
     </row>
     <row r="63">
@@ -5522,34 +5242,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Net change in cash during the year</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>ChangesInCash</t>
-        </is>
-      </c>
+          <t>Investment in equipment</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F63" s="5" t="n">
+        <v>-0.12207</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-2.06671</v>
+        <v>-0.148032</v>
       </c>
       <c r="H63" s="5" t="n">
-        <v>-3.504554</v>
+        <v>-0.185155</v>
       </c>
     </row>
     <row r="64">
@@ -5560,17 +5274,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cash, beginning of the year</t>
+          <t>Net cash used in investing activities</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>BeginningCashPosition</t>
+          <t>InvestingCashFlow</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5584,10 +5298,10 @@
         </is>
       </c>
       <c r="G64" s="5" t="n">
-        <v>6.463991</v>
+        <v>-0.828466</v>
       </c>
       <c r="H64" s="5" t="n">
-        <v>4.397281</v>
+        <v>-1.255737</v>
       </c>
     </row>
     <row r="65">
@@ -5603,29 +5317,21 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Cash, end of the year $</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Repayments of loans</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>-0.614499</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-0.003876</v>
       </c>
       <c r="G65" s="5" t="n">
-        <v>4.397281</v>
+        <v>-0.007752</v>
       </c>
       <c r="H65" s="5" t="n">
-        <v>0.892727</v>
+        <v>-0.007752</v>
       </c>
     </row>
     <row r="66">
@@ -5634,28 +5340,32 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Six months ended September 30, 2022 September</t>
+          <t>Proceeds from issuance of promissory notes and convertible debentures</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>0.002021</v>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>3e-05</v>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>5.54533</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="67">
@@ -5666,34 +5376,30 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>OPERATING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Net loss for the period $</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>NetIncomeFromContinuingOperations</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="n">
-        <v>-4.784801</v>
-      </c>
-      <c r="F67" s="5" t="n">
-        <v>-9.53759</v>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceeds from issuance of equity instruments</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>11.691257</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>9.839456999999999</v>
       </c>
     </row>
     <row r="68">
@@ -5704,27 +5410,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Gain on conversion of SAFE</t>
+          <t>Proceeds from obligation to issue shares</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" s="5" t="n">
-        <v>-0.118378</v>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G68" s="5" t="n">
+        <v>0.083456</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5740,17 +5446,19 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Listing expense</t>
+          <t>Proceeds from issuance of units</t>
         </is>
       </c>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" s="5" t="n">
-        <v>5.352659</v>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -5762,10 +5470,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H69" s="5" t="n">
+        <v>17.518269</v>
       </c>
     </row>
     <row r="70">
@@ -5776,30 +5482,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Interest expense</t>
+          <t>Private placement issuance costs</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
-      <c r="E70" s="5" t="n">
-        <v>0.131852</v>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F70" s="5" t="n">
-        <v>0.012105</v>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.77918</v>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>-1.308785</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>-1.697576</v>
       </c>
     </row>
     <row r="71">
@@ -5810,36 +5514,32 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Gain on the settlement of accounts payable</t>
+          <t>Lease payments</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="n">
-        <v>-0.377737</v>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.065709</v>
+      </c>
+      <c r="G71" s="5" t="n">
+        <v>-0.131776</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>-0.113978</v>
       </c>
     </row>
     <row r="72">
@@ -5850,32 +5550,30 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Items not involving cash</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Issuance of warrants for services</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="n">
+        <v>0.440501</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>0.371507</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>10.716218</v>
+      </c>
+      <c r="G72" s="5" t="n">
+        <v>15.87173</v>
+      </c>
+      <c r="H72" s="5" t="n">
+        <v>27.53842</v>
       </c>
     </row>
     <row r="73">
@@ -5886,32 +5584,30 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Net changes in non-cash working capital items</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Due from related parties</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange effect on cash</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>EffectOfExchangeRateChanges</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="n">
+        <v>-0.010386</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>-0.233697</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.511057</v>
+      </c>
+      <c r="G73" s="5" t="n">
+        <v>-0.402341</v>
+      </c>
+      <c r="H73" s="5" t="n">
+        <v>-0.347839</v>
       </c>
     </row>
     <row r="74">
@@ -5922,32 +5618,34 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cash acquired on RTO</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
-      <c r="E74" s="5" t="n">
-        <v>1.295204</v>
+          <t>Net change in cash during the year</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G74" s="5" t="n">
+        <v>-2.06671</v>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>-3.504554</v>
       </c>
     </row>
     <row r="75">
@@ -5958,34 +5656,34 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>INVESTING ACTIVITIES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Net cash provided (used in) investing activities</t>
+          <t>Cash, beginning of the year</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>InvestingCashFlow</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>1.295204</v>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-0.12207</v>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" s="5" t="n">
+        <v>6.463991</v>
+      </c>
+      <c r="H75" s="5" t="n">
+        <v>4.397281</v>
       </c>
     </row>
     <row r="76">
@@ -6001,27 +5699,29 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Proceed from issuance of loans</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
-      <c r="E76" s="5" t="n">
-        <v>0.275</v>
+          <t>Cash, end of the year $</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G76" s="5" t="n">
+        <v>4.397281</v>
+      </c>
+      <c r="H76" s="5" t="n">
+        <v>0.892727</v>
       </c>
     </row>
     <row r="77">
@@ -6030,22 +5730,18 @@
           <t>cash_flow</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>FINANCING ACTIVITIES</t>
-        </is>
-      </c>
+      <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Issuance of units</t>
+          <t>Six months ended September 30, 2022 September</t>
         </is>
       </c>
       <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>0.28</v>
+        <v>0.002021</v>
       </c>
       <c r="F77" s="5" t="n">
-        <v>11.564983</v>
+        <v>3e-05</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6066,22 +5762,24 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Advances received from VTI prior to RTO</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>Net loss for the period $</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E78" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-4.784801</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-9.53759</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -6102,20 +5800,22 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Net change in cash and restricted cash during the period</t>
+          <t>Gain on conversion of SAFE</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
-        <v>0.173676</v>
-      </c>
-      <c r="F79" s="5" t="n">
-        <v>1.512578</v>
+        <v>-0.118378</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -6136,24 +5836,22 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cash and restricted cash, beginning of the period</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>BeginningCashPosition</t>
-        </is>
-      </c>
+          <t>Listing expense</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" s="5" t="n">
-        <v>0.871285</v>
-      </c>
-      <c r="F80" s="5" t="n">
-        <v>6.463991</v>
+        <v>5.352659</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -6174,24 +5872,20 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FINANCING ACTIVITIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Cash and restricted cash, end of the period $</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>EndCashPosition</t>
-        </is>
-      </c>
+          <t>Interest expense</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" s="5" t="n">
-        <v>1.044961</v>
+        <v>0.131852</v>
       </c>
       <c r="F81" s="5" t="n">
-        <v>7.976569</v>
+        <v>0.012105</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -6212,20 +5906,26 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1. NATURE OF BUSINESS AND GOING CONCERN</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>1. NATURE OF BUSINESS AND GOING CONCERN total</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Gain on the settlement of accounts payable</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E82" s="5" t="n">
-        <v>0.00202</v>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>1.9e-05</v>
+        <v>-0.377737</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -6246,20 +5946,22 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2. SUMMARY OF SIGNIFICANT ACCOUNTING POLICIES</t>
+          <t>Items not involving cash</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Company's audited annual consolidated financial statements for the fiscal year ended March</t>
+          <t>Issuance of warrants for services</t>
         </is>
       </c>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" s="5" t="n">
-        <v>0.002022</v>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.371507</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -6280,20 +5982,22 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2. SUMMARY OF SIGNIFICANT ACCOUNTING POLICIES</t>
+          <t>Net changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>which have been prepared in accordance with International Financial Reporting Standards (“IFRS”). resolution from the Board of Directors on November</t>
+          <t>Due from related parties</t>
         </is>
       </c>
       <c r="D84" t="inlineStr"/>
-      <c r="E84" s="5" t="n">
-        <v>0.002022</v>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>1.4e-05</v>
+        <v>-0.233697</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -6314,20 +6018,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>b)  Basis of preparation</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>used in the preparation of the audited financial statements as of March 31, 2022. The accompanying audited annual consolidated financial statements for the year ended March</t>
+          <t>Cash acquired on RTO</t>
         </is>
       </c>
       <c r="D85" t="inlineStr"/>
       <c r="E85" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>1.295204</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -6348,20 +6054,24 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>could differ from these estimates.</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>The significant judgements made by management in the Company’s accounting policies and key sources statements for the year ended March</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
+          <t>Net cash provided (used in) investing activities</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
       <c r="E86" s="5" t="n">
-        <v>0.002022</v>
+        <v>1.295204</v>
       </c>
       <c r="F86" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.12207</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -6377,405 +6087,387 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>REVENUE 4 $</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Proceed from issuance of loans</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>0.275</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G87" s="5" t="n">
-        <v>1.605104</v>
-      </c>
-      <c r="H87" s="5" t="n">
-        <v>1.966731</v>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>COST OF REVENUE</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>CostOfRevenue</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G88" s="5" t="n">
-        <v>1.135548</v>
-      </c>
-      <c r="H88" s="5" t="n">
-        <v>1.69917</v>
+          <t>Issuance of units</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" s="5" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>11.564983</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Accounting fees</t>
+          <t>Advances received from VTI prior to RTO</t>
         </is>
       </c>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E89" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G89" s="5" t="n">
-        <v>0.615546</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>0.538394</v>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Consulting fees</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>1.118877</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>4.146232</v>
+          <t>Net change in cash and restricted cash during the period</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>0.173676</v>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>1.512578</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Depreciation 17, 18</t>
+          <t>Cash and restricted cash, beginning of the period</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>0.23613</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>0.261747</v>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="n">
+        <v>0.871285</v>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>6.463991</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>FINANCING ACTIVITIES</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Investor relations</t>
+          <t>Cash and restricted cash, end of the period $</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>1.325615</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>2.652392</v>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="n">
+        <v>1.044961</v>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>7.976569</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>1. NATURE OF BUSINESS AND GOING CONCERN</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Legal fees</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>1.127083</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>2.015619</v>
+          <t>1. NATURE OF BUSINESS AND GOING CONCERN total</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" s="5" t="n">
+        <v>0.00202</v>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>1.9e-05</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>2. SUMMARY OF SIGNIFICANT ACCOUNTING POLICIES</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Management fees 10</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Company's audited annual consolidated financial statements for the fiscal year ended March</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F94" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="H94" s="5" t="n">
-        <v>0.041067</v>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>2. SUMMARY OF SIGNIFICANT ACCOUNTING POLICIES</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Marketing</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="n">
-        <v>1.757983</v>
-      </c>
-      <c r="H95" s="5" t="n">
-        <v>4.328186</v>
+          <t>which have been prepared in accordance with International Financial Reporting Standards (“IFRS”). resolution from the Board of Directors on November</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F95" s="5" t="n">
+        <v>1.4e-05</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>b)  Basis of preparation</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Office and general</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G96" s="5" t="n">
-        <v>1.25785</v>
-      </c>
-      <c r="H96" s="5" t="n">
-        <v>1.709991</v>
+          <t>used in the preparation of the audited financial statements as of March 31, 2022. The accompanying audited annual consolidated financial statements for the year ended March</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F96" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>could differ from these estimates.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Personnel expenses 10</t>
+          <t>The significant judgements made by management in the Company’s accounting policies and key sources statements for the year ended March</t>
         </is>
       </c>
       <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="n">
-        <v>2.954123</v>
-      </c>
-      <c r="H97" s="5" t="n">
-        <v>3.713861</v>
+      <c r="E97" s="5" t="n">
+        <v>0.002022</v>
+      </c>
+      <c r="F97" s="5" t="n">
+        <v>3.1e-05</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="98">
@@ -6784,19 +6476,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B98" t="inlineStr"/>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Rent</t>
+          <t>REVENUE 4 $</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6810,10 +6498,10 @@
         </is>
       </c>
       <c r="G98" s="5" t="n">
-        <v>0.027549</v>
+        <v>1.605104</v>
       </c>
       <c r="H98" s="5" t="n">
-        <v>0.026838</v>
+        <v>1.966731</v>
       </c>
     </row>
     <row r="99">
@@ -6822,19 +6510,15 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B99" t="inlineStr"/>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Research and development</t>
+          <t>COST OF REVENUE</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>ResearchAndDevelopment</t>
+          <t>CostOfRevenue</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6848,10 +6532,10 @@
         </is>
       </c>
       <c r="G99" s="5" t="n">
-        <v>5.88154</v>
+        <v>1.135548</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>12.024288</v>
+        <v>1.69917</v>
       </c>
     </row>
     <row r="100">
@@ -6867,7 +6551,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Share based payments 8, 10</t>
+          <t>Accounting fees</t>
         </is>
       </c>
       <c r="D100" t="inlineStr"/>
@@ -6882,10 +6566,10 @@
         </is>
       </c>
       <c r="G100" s="5" t="n">
-        <v>2.706068</v>
+        <v>0.615546</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>7.850119</v>
+        <v>0.538394</v>
       </c>
     </row>
     <row r="101">
@@ -6901,10 +6585,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Travel and meals</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
+          <t>Consulting fees</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -6916,10 +6604,10 @@
         </is>
       </c>
       <c r="G101" s="5" t="n">
-        <v>0.942587</v>
+        <v>1.118877</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>1.098984</v>
+        <v>4.146232</v>
       </c>
     </row>
     <row r="102">
@@ -6935,25 +6623,29 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Depreciation 17, 18</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="n">
-        <v>1.798976</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>9.949579</v>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G102" s="5" t="n">
-        <v>19.950951</v>
+        <v>0.23613</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>40.407718</v>
+        <v>0.261747</v>
       </c>
     </row>
     <row r="103">
@@ -6964,17 +6656,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Interest expense 7, 15, 19</t>
+          <t>Investor relations</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>InterestExpenseOperating</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6988,10 +6680,10 @@
         </is>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.095167</v>
+        <v>1.325615</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>-0.348441</v>
+        <v>2.652392</v>
       </c>
     </row>
     <row r="104">
@@ -7002,15 +6694,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Accretion expense 15</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
+          <t>Legal fees</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
           <t>-</t>
@@ -7022,10 +6718,10 @@
         </is>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.036626</v>
+        <v>1.127083</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.203918</v>
+        <v>2.015619</v>
       </c>
     </row>
     <row r="105">
@@ -7036,17 +6732,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Other income 21</t>
+          <t>Management fees 10</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -7059,11 +6755,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G105" s="5" t="n">
-        <v>0.024305</v>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H105" s="5" t="n">
-        <v>0.240293</v>
+        <v>0.041067</v>
       </c>
     </row>
     <row r="106">
@@ -7074,15 +6772,19 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Legal claim expense 26</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
+          <t>Marketing</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E106" t="inlineStr">
         <is>
           <t>-</t>
@@ -7093,13 +6795,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G106" s="5" t="n">
+        <v>1.757983</v>
       </c>
       <c r="H106" s="5" t="n">
-        <v>-6.307258</v>
+        <v>4.328186</v>
       </c>
     </row>
     <row r="107">
@@ -7110,15 +6810,19 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Grant income 3</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
+          <t>Office and general</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
           <t>-</t>
@@ -7130,10 +6834,10 @@
         </is>
       </c>
       <c r="G107" s="5" t="n">
-        <v>0.136045</v>
+        <v>1.25785</v>
       </c>
       <c r="H107" s="5" t="n">
-        <v>0.154709</v>
+        <v>1.709991</v>
       </c>
     </row>
     <row r="108">
@@ -7144,19 +6848,15 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>LOSS BEFORE INCOME TAXES</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>PretaxIncome</t>
-        </is>
-      </c>
+          <t>Personnel expenses 10</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -7168,10 +6868,10 @@
         </is>
       </c>
       <c r="G108" s="5" t="n">
-        <v>-19.452838</v>
+        <v>2.954123</v>
       </c>
       <c r="H108" s="5" t="n">
-        <v>-46.604772</v>
+        <v>3.713861</v>
       </c>
     </row>
     <row r="109">
@@ -7182,17 +6882,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Income taxes 27</t>
+          <t>Rent</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>TaxProvision</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -7206,10 +6906,10 @@
         </is>
       </c>
       <c r="G109" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.027549</v>
       </c>
       <c r="H109" s="5" t="n">
-        <v>-0.002513</v>
+        <v>0.026838</v>
       </c>
     </row>
     <row r="110">
@@ -7220,17 +6920,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>NET LOSS</t>
+          <t>Research and development</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>ResearchAndDevelopment</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -7244,10 +6944,10 @@
         </is>
       </c>
       <c r="G110" s="5" t="n">
-        <v>-19.458438</v>
+        <v>5.88154</v>
       </c>
       <c r="H110" s="5" t="n">
-        <v>-46.607285</v>
+        <v>12.024288</v>
       </c>
     </row>
     <row r="111">
@@ -7258,12 +6958,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Foreign exchange difference</t>
+          <t>Share based payments 8, 10</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -7278,10 +6978,10 @@
         </is>
       </c>
       <c r="G111" s="5" t="n">
-        <v>-0.402341</v>
+        <v>2.706068</v>
       </c>
       <c r="H111" s="5" t="n">
-        <v>-0.284431</v>
+        <v>7.850119</v>
       </c>
     </row>
     <row r="112">
@@ -7292,12 +6992,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>NET COMPREHENSIVE LOSS $</t>
+          <t>Travel and meals</t>
         </is>
       </c>
       <c r="D112" t="inlineStr"/>
@@ -7312,10 +7012,10 @@
         </is>
       </c>
       <c r="G112" s="5" t="n">
-        <v>-19.860779</v>
+        <v>0.942587</v>
       </c>
       <c r="H112" s="5" t="n">
-        <v>-46.891716</v>
+        <v>1.098984</v>
       </c>
     </row>
     <row r="113">
@@ -7326,30 +7026,30 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Loss Per Class A Subordinate Voting Shares - Basic and Diluted $</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="n">
+        <v>1.798976</v>
+      </c>
+      <c r="F113" s="5" t="n">
+        <v>9.949579</v>
       </c>
       <c r="G113" s="5" t="n">
-        <v>-1.8e-07</v>
+        <v>19.950951</v>
       </c>
       <c r="H113" s="5" t="n">
-        <v>-3.4e-07</v>
+        <v>40.407718</v>
       </c>
     </row>
     <row r="114">
@@ -7365,10 +7065,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Loss Per Class B Proportionate Voting Shares - Basic and Diluted $</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
+          <t>Interest expense 7, 15, 19</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>InterestExpenseOperating</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -7380,10 +7084,10 @@
         </is>
       </c>
       <c r="G114" s="5" t="n">
-        <v>-1.1e-06</v>
+        <v>-0.095167</v>
       </c>
       <c r="H114" s="5" t="n">
-        <v>-2.11e-06</v>
+        <v>-0.348441</v>
       </c>
     </row>
     <row r="115">
@@ -7399,7 +7103,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Class A Subordinate Voting Shares - Basic and Diluted</t>
+          <t>Accretion expense 15</t>
         </is>
       </c>
       <c r="D115" t="inlineStr"/>
@@ -7414,10 +7118,10 @@
         </is>
       </c>
       <c r="G115" s="5" t="n">
-        <v>49.836021</v>
+        <v>-0.036626</v>
       </c>
       <c r="H115" s="5" t="n">
-        <v>76.469216</v>
+        <v>-0.203918</v>
       </c>
     </row>
     <row r="116">
@@ -7433,10 +7137,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Class B Proportionate Voting Shares - Basic and Diluted</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
+          <t>Other income 21</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -7448,10 +7156,10 @@
         </is>
       </c>
       <c r="G116" s="5" t="n">
-        <v>10</v>
+        <v>0.024305</v>
       </c>
       <c r="H116" s="5" t="n">
-        <v>10</v>
+        <v>0.240293</v>
       </c>
     </row>
     <row r="117">
@@ -7462,12 +7170,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Common   Common                  Contributed  to Issue    Comprehensive                 Equity</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2022 10,000,000 40,382,512 $ 20,384,147 $ 1,583,782 $ - $ (234,186) $</t>
+          <t>Legal claim expense 26</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -7481,11 +7189,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G117" s="5" t="n">
-        <v>6.715939</v>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H117" s="5" t="n">
-        <v>-15.017804</v>
+        <v>-6.307258</v>
       </c>
     </row>
     <row r="118">
@@ -7496,12 +7206,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units granted - - - 2,403,531 - -</t>
+          <t>Grant income 3</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
@@ -7516,12 +7226,10 @@
         </is>
       </c>
       <c r="G118" s="5" t="n">
-        <v>2.403531</v>
-      </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.136045</v>
+      </c>
+      <c r="H118" s="5" t="n">
+        <v>0.154709</v>
       </c>
     </row>
     <row r="119">
@@ -7532,15 +7240,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Issuance of warrants for services - - - 371,507 - -</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
+          <t>LOSS BEFORE INCOME TAXES</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>PretaxIncome</t>
+        </is>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
           <t>-</t>
@@ -7552,12 +7264,10 @@
         </is>
       </c>
       <c r="G119" s="5" t="n">
-        <v>0.371507</v>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.452838</v>
+      </c>
+      <c r="H119" s="5" t="n">
+        <v>-46.604772</v>
       </c>
     </row>
     <row r="120">
@@ -7568,15 +7278,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Issuance of units for cash - 14,907,030 11,333,681 231,302 - -</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
+          <t>Income taxes 27</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -7588,12 +7302,10 @@
         </is>
       </c>
       <c r="G120" s="5" t="n">
-        <v>11.564983</v>
-      </c>
-      <c r="H120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.0056</v>
+      </c>
+      <c r="H120" s="5" t="n">
+        <v>-0.002513</v>
       </c>
     </row>
     <row r="121">
@@ -7604,15 +7316,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Private placement issuance costs - 291,325 (1,629,988) 807,214 - -</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
+          <t>NET LOSS</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E121" t="inlineStr">
         <is>
           <t>-</t>
@@ -7624,12 +7340,10 @@
         </is>
       </c>
       <c r="G121" s="5" t="n">
-        <v>-0.822774</v>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.458438</v>
+      </c>
+      <c r="H121" s="5" t="n">
+        <v>-46.607285</v>
       </c>
     </row>
     <row r="122">
@@ -7640,12 +7354,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants - 225,070 176,339 (50,065) - -</t>
+          <t>Foreign exchange difference</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
@@ -7660,12 +7374,10 @@
         </is>
       </c>
       <c r="G122" s="5" t="n">
-        <v>0.126274</v>
-      </c>
-      <c r="H122" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.402341</v>
+      </c>
+      <c r="H122" s="5" t="n">
+        <v>-0.284431</v>
       </c>
     </row>
     <row r="123">
@@ -7676,12 +7388,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Stock options and restricted share units</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Subscriptions received - - - - 83,456 -</t>
+          <t>NET COMPREHENSIVE LOSS $</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
@@ -7696,12 +7408,10 @@
         </is>
       </c>
       <c r="G123" s="5" t="n">
-        <v>0.083456</v>
-      </c>
-      <c r="H123" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.860779</v>
+      </c>
+      <c r="H123" s="5" t="n">
+        <v>-46.891716</v>
       </c>
     </row>
     <row r="124">
@@ -7712,12 +7422,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component, net of issuance costs - - - 86,465 - -</t>
+          <t>Loss Per Class A Subordinate Voting Shares - Basic and Diluted $</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
@@ -7732,12 +7442,10 @@
         </is>
       </c>
       <c r="G124" s="5" t="n">
-        <v>0.086465</v>
-      </c>
-      <c r="H124" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.8e-07</v>
+      </c>
+      <c r="H124" s="5" t="n">
+        <v>-3.4e-07</v>
       </c>
     </row>
     <row r="125">
@@ -7748,12 +7456,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Convertible debentures issuance costs - - - 172,771 - -</t>
+          <t>Loss Per Class B Proportionate Voting Shares - Basic and Diluted $</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
@@ -7768,12 +7476,10 @@
         </is>
       </c>
       <c r="G125" s="5" t="n">
-        <v>0.172771</v>
-      </c>
-      <c r="H125" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1.1e-06</v>
+      </c>
+      <c r="H125" s="5" t="n">
+        <v>-2.11e-06</v>
       </c>
     </row>
     <row r="126">
@@ -7784,12 +7490,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Foreign exchange difference - - - - - (402,341)</t>
+          <t>Weighted Average Number of Class A Subordinate Voting Shares - Basic and Diluted</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
@@ -7804,12 +7510,10 @@
         </is>
       </c>
       <c r="G126" s="5" t="n">
-        <v>-0.402341</v>
-      </c>
-      <c r="H126" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>49.836021</v>
+      </c>
+      <c r="H126" s="5" t="n">
+        <v>76.469216</v>
       </c>
     </row>
     <row r="127">
@@ -7820,19 +7524,15 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>OTHER ITEMS</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Net loss - - - - - -</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Weighted Average Number of Class B Proportionate Voting Shares - Basic and Diluted</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -7844,10 +7544,10 @@
         </is>
       </c>
       <c r="G127" s="5" t="n">
-        <v>-19.458438</v>
+        <v>10</v>
       </c>
       <c r="H127" s="5" t="n">
-        <v>-19.458438</v>
+        <v>10</v>
       </c>
     </row>
     <row r="128">
@@ -7858,12 +7558,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Common   Common                  Contributed  to Issue    Comprehensive                 Equity</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2023 10,000,000 55,805,937 30,264,179 5,606,507 83,456 (636,527)</t>
+          <t>Balance, March 31, 2022 10,000,000 40,382,512 $ 20,384,147 $ 1,583,782 $ - $ (234,186) $</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
@@ -7878,10 +7578,10 @@
         </is>
       </c>
       <c r="G128" s="5" t="n">
-        <v>0.841373</v>
+        <v>6.715939</v>
       </c>
       <c r="H128" s="5" t="n">
-        <v>-34.476242</v>
+        <v>-15.017804</v>
       </c>
     </row>
     <row r="129">
@@ -7892,12 +7592,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Stock options and restricted share units</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Exercise of options and warrants - 13,949,121 11,042,575 (1,119,662) (83,456) -</t>
+          <t>Stock options and restricted share units granted - - - 2,403,531 - -</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
@@ -7912,7 +7612,7 @@
         </is>
       </c>
       <c r="G129" s="5" t="n">
-        <v>9.839456999999999</v>
+        <v>2.403531</v>
       </c>
       <c r="H129" t="inlineStr">
         <is>
@@ -7928,12 +7628,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Stock options and restricted share units</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Issuance of units for cash - 4,878,048 7,491,999 - - -</t>
+          <t>Issuance of warrants for services - - - 371,507 - -</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
@@ -7948,7 +7648,7 @@
         </is>
       </c>
       <c r="G130" s="5" t="n">
-        <v>7.491999</v>
+        <v>0.371507</v>
       </c>
       <c r="H130" t="inlineStr">
         <is>
@@ -7964,12 +7664,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Stock options and restricted share units</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Private placement issuance costs - 50,000 (1,593,214) 697,807 - -</t>
+          <t>Issuance of units for cash - 14,907,030 11,333,681 231,302 - -</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
@@ -7984,7 +7684,7 @@
         </is>
       </c>
       <c r="G131" s="5" t="n">
-        <v>-0.895407</v>
+        <v>11.564983</v>
       </c>
       <c r="H131" t="inlineStr">
         <is>
@@ -8000,12 +7700,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Stock options and restricted share units</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Conversion of convertible debentures (net) - 4,372,648 5,699,420 (98,048) - -</t>
+          <t>Private placement issuance costs - 291,325 (1,629,988) 807,214 - -</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
@@ -8020,7 +7720,7 @@
         </is>
       </c>
       <c r="G132" s="5" t="n">
-        <v>5.601372</v>
+        <v>-0.822774</v>
       </c>
       <c r="H132" t="inlineStr">
         <is>
@@ -8036,12 +7736,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Stock options and restricted share units</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Stock options granted - - - 6,934,678 - -</t>
+          <t>Exercise of options and warrants - 225,070 176,339 (50,065) - -</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
@@ -8056,7 +7756,7 @@
         </is>
       </c>
       <c r="G133" s="5" t="n">
-        <v>6.934678</v>
+        <v>0.126274</v>
       </c>
       <c r="H133" t="inlineStr">
         <is>
@@ -8072,12 +7772,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Convertible debentures equity component,</t>
+          <t>Stock options and restricted share units</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Modification of finders' warrants - - - 440,604 - -</t>
+          <t>Subscriptions received - - - - 83,456 -</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
@@ -8092,7 +7792,7 @@
         </is>
       </c>
       <c r="G134" s="5" t="n">
-        <v>0.440604</v>
+        <v>0.083456</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
@@ -8113,7 +7813,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Special warrants issued - - - - 10,026,270 -</t>
+          <t>Convertible debentures equity component, net of issuance costs - - - 86,465 - -</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
@@ -8128,7 +7828,7 @@
         </is>
       </c>
       <c r="G135" s="5" t="n">
-        <v>10.02627</v>
+        <v>0.086465</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
@@ -8149,7 +7849,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Special warrants issuance costs - - - 782,626 (1,584,795) -</t>
+          <t>Convertible debentures issuance costs - - - 172,771 - -</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
@@ -8164,7 +7864,7 @@
         </is>
       </c>
       <c r="G136" s="5" t="n">
-        <v>-0.802169</v>
+        <v>0.172771</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
@@ -8185,7 +7885,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Special warrants converted to shares - 6,612,849 8,441,475 - (8,441,475) -</t>
+          <t>Foreign exchange difference - - - - - (402,341)</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
@@ -8199,10 +7899,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G137" s="5" t="n">
+        <v>-0.402341</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
@@ -8223,10 +7921,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Issuance of shares for settlement - 200,000 198,801 - - -</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr"/>
+          <t>Net loss - - - - - -</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -8238,12 +7940,10 @@
         </is>
       </c>
       <c r="G138" s="5" t="n">
-        <v>0.198801</v>
-      </c>
-      <c r="H138" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-19.458438</v>
+      </c>
+      <c r="H138" s="5" t="n">
+        <v>-19.458438</v>
       </c>
     </row>
     <row r="139">
@@ -8259,7 +7959,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SAFE conversion to shares - 675,000 1,025,000 - - -</t>
+          <t>Balance, March 31, 2023 10,000,000 55,805,937 30,264,179 5,606,507 83,456 (636,527)</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
@@ -8274,12 +7974,10 @@
         </is>
       </c>
       <c r="G139" s="5" t="n">
-        <v>1.025</v>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.841373</v>
+      </c>
+      <c r="H139" s="5" t="n">
+        <v>-34.476242</v>
       </c>
     </row>
     <row r="140">
@@ -8295,7 +7993,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Foreign exchange difference - - - - - (284,431)</t>
+          <t>Exercise of options and warrants - 13,949,121 11,042,575 (1,119,662) (83,456) -</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
@@ -8310,7 +8008,7 @@
         </is>
       </c>
       <c r="G140" s="5" t="n">
-        <v>-0.284431</v>
+        <v>9.839456999999999</v>
       </c>
       <c r="H140" t="inlineStr">
         <is>
@@ -8331,7 +8029,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Balance, March 31, 2024 10,000,000 86,543,603 $ 62,570,235 $ 13,244,512 $ - $ (920,958) $</t>
+          <t>Issuance of units for cash - 4,878,048 7,491,999 - - -</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
@@ -8346,10 +8044,12 @@
         </is>
       </c>
       <c r="G141" s="5" t="n">
-        <v>-6.189738</v>
-      </c>
-      <c r="H141" s="5" t="n">
-        <v>-81.083527</v>
+        <v>7.491999</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="142">
@@ -8358,27 +8058,29 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr"/>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Convertible debentures equity component,</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>REVENUE 4 $ 278,547 $ 2,087,803 $</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>TotalRevenue</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="n">
-        <v>2.147803</v>
-      </c>
-      <c r="F142" s="5" t="n">
-        <v>0.652066</v>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Private placement issuance costs - 50,000 (1,593,214) 697,807 - -</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G142" s="5" t="n">
+        <v>-0.895407</v>
       </c>
       <c r="H142" t="inlineStr">
         <is>
@@ -8392,23 +8094,29 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr"/>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Convertible debentures equity component,</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>COST OF REVENUE (131,141) (214,081)</t>
+          <t>Conversion of convertible debentures (net) - 4,372,648 5,699,420 (98,048) - -</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
-      <c r="E143" s="5" t="n">
-        <v>-0.473975</v>
-      </c>
-      <c r="F143" s="5" t="n">
-        <v>-0.404926</v>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G143" s="5" t="n">
+        <v>5.601372</v>
       </c>
       <c r="H143" t="inlineStr">
         <is>
@@ -8424,25 +8132,27 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Accounting fees 146,140 46,236</t>
+          <t>Stock options granted - - - 6,934,678 - -</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
-      <c r="E144" s="5" t="n">
-        <v>0.064902</v>
-      </c>
-      <c r="F144" s="5" t="n">
-        <v>0.374229</v>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G144" s="5" t="n">
+        <v>6.934678</v>
       </c>
       <c r="H144" t="inlineStr">
         <is>
@@ -8458,29 +8168,27 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Consulting fees 95,121 142,658</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="n">
-        <v>0.279914</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>0.290735</v>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Modification of finders' warrants - - - 440,604 - -</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G145" s="5" t="n">
+        <v>0.440604</v>
       </c>
       <c r="H145" t="inlineStr">
         <is>
@@ -8496,12 +8204,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Depreciation 15, 16 59,683 -</t>
+          <t>Special warrants issued - - - - 10,026,270 -</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
@@ -8510,13 +8218,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F146" s="5" t="n">
-        <v>0.11621</v>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G146" s="5" t="n">
+        <v>10.02627</v>
       </c>
       <c r="H146" t="inlineStr">
         <is>
@@ -8532,29 +8240,27 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Investor relations 533,578 454</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="n">
-        <v>0.000454</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>0.58049</v>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Special warrants issuance costs - - - 782,626 (1,584,795) -</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G147" s="5" t="n">
+        <v>-0.802169</v>
       </c>
       <c r="H147" t="inlineStr">
         <is>
@@ -8570,24 +8276,24 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Legal fees 164,052 58,474</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="n">
-        <v>0.173065</v>
-      </c>
-      <c r="F148" s="5" t="n">
-        <v>0.500122</v>
+          <t>Special warrants converted to shares - 6,612,849 8,441,475 - (8,441,475) -</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -8608,31 +8314,27 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Management fees 10 - 454,490</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="n">
-        <v>0.8599059999999999</v>
+          <t>Issuance of shares for settlement - 200,000 198,801 - - -</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G149" s="5" t="n">
+        <v>0.198801</v>
       </c>
       <c r="H149" t="inlineStr">
         <is>
@@ -8648,29 +8350,27 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Marketing 368,517 180,000</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>OtherOperatingExpenses</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F150" s="5" t="n">
-        <v>1.077647</v>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SAFE conversion to shares - 675,000 1,025,000 - - -</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G150" s="5" t="n">
+        <v>1.025</v>
       </c>
       <c r="H150" t="inlineStr">
         <is>
@@ -8686,29 +8386,27 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Office and general 313,494 43,902</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E151" s="5" t="n">
-        <v>0.06505900000000001</v>
-      </c>
-      <c r="F151" s="5" t="n">
-        <v>0.548969</v>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Foreign exchange difference - - - - - (284,431)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G151" s="5" t="n">
+        <v>-0.284431</v>
       </c>
       <c r="H151" t="inlineStr">
         <is>
@@ -8724,30 +8422,30 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Convertible debentures equity component,</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Personnel expenses 10 731,465 28,000</t>
+          <t>Balance, March 31, 2024 10,000,000 86,543,603 $ 62,570,235 $ 13,244,512 $ - $ (920,958) $</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" s="5" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="F152" s="5" t="n">
-        <v>1.5807</v>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G152" s="5" t="n">
+        <v>-6.189738</v>
+      </c>
+      <c r="H152" s="5" t="n">
+        <v>-81.083527</v>
       </c>
     </row>
     <row r="153">
@@ -8756,26 +8454,22 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B153" t="inlineStr"/>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Rent 17 11,274 28,301</t>
+          <t>REVENUE 4 $ 278,547 $ 2,087,803 $</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>TotalRevenue</t>
         </is>
       </c>
       <c r="E153" s="5" t="n">
-        <v>0.043511</v>
+        <v>2.147803</v>
       </c>
       <c r="F153" s="5" t="n">
-        <v>0.013494</v>
+        <v>0.652066</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -8794,24 +8488,18 @@
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>EXPENSES</t>
-        </is>
-      </c>
+      <c r="B154" t="inlineStr"/>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Research and development 1,518,954 -</t>
+          <t>COST OF REVENUE (131,141) (214,081)</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E154" s="5" t="n">
+        <v>-0.473975</v>
       </c>
       <c r="F154" s="5" t="n">
-        <v>2.816176</v>
+        <v>-0.404926</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -8837,17 +8525,15 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Share based payments 8, 10 491,659 -</t>
+          <t>Accounting fees 146,140 46,236</t>
         </is>
       </c>
       <c r="D155" t="inlineStr"/>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E155" s="5" t="n">
+        <v>0.064902</v>
       </c>
       <c r="F155" s="5" t="n">
-        <v>1.5549</v>
+        <v>0.374229</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -8873,15 +8559,19 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Travel and meals 149,800 39,676</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr"/>
+          <t>Consulting fees 95,121 142,658</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E156" s="5" t="n">
-        <v>0.046165</v>
+        <v>0.279914</v>
       </c>
       <c r="F156" s="5" t="n">
-        <v>0.495907</v>
+        <v>0.290735</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -8902,20 +8592,22 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Interest expense 7, 10 (9,351) (81,981)</t>
+          <t>Depreciation 15, 16 59,683 -</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
-      <c r="E157" s="5" t="n">
-        <v>-0.131852</v>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F157" s="5" t="n">
-        <v>-0.015739</v>
+        <v>0.11621</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -8936,24 +8628,24 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Other income 18 3,288 118,378</t>
+          <t>Investor relations 533,578 454</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E158" s="5" t="n">
-        <v>0.496115</v>
+        <v>0.000454</v>
       </c>
       <c r="F158" s="5" t="n">
-        <v>0.01699</v>
+        <v>0.58049</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -8974,20 +8666,24 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Grant income 3 92,031 166,976</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr"/>
+          <t>Legal fees 164,052 58,474</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E159" s="5" t="n">
-        <v>0.328743</v>
+        <v>0.173065</v>
       </c>
       <c r="F159" s="5" t="n">
-        <v>0.163598</v>
+        <v>0.500122</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -9008,17 +8704,21 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Listing expense 24 - (5,352,659)</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr"/>
+          <t>Management fees 10 - 454,490</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E160" s="5" t="n">
-        <v>-5.352659</v>
+        <v>0.8599059999999999</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -9044,20 +8744,24 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>NET LOSS (4,350,363) (4,297,755)</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Marketing 368,517 180,000</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E161" s="5" t="n">
-        <v>-4.784801</v>
+        <v>0.21</v>
       </c>
       <c r="F161" s="5" t="n">
-        <v>-9.53759</v>
+        <v>1.077647</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -9078,20 +8782,24 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Foreign exchange difference (510,196) (10,386)</t>
-        </is>
-      </c>
-      <c r="D162" t="inlineStr"/>
+          <t>Office and general 313,494 43,902</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E162" s="5" t="n">
-        <v>-0.010386</v>
+        <v>0.06505900000000001</v>
       </c>
       <c r="F162" s="5" t="n">
-        <v>-0.511057</v>
+        <v>0.548969</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -9112,20 +8820,20 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>NET COMPREHENSIVE LOSS $ (4,860,559) $ (4,308,141) $</t>
+          <t>Personnel expenses 10 731,465 28,000</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" s="5" t="n">
-        <v>-4.795187</v>
+        <v>0.056</v>
       </c>
       <c r="F163" s="5" t="n">
-        <v>-10.048647</v>
+        <v>1.5807</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -9146,20 +8854,24 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Loss Per Class A Subordinate Voting Shares - Basic and Diluted $ (0.04) $ (0.05) $</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr"/>
+          <t>Rent 17 11,274 28,301</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E164" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>0.043511</v>
       </c>
       <c r="F164" s="5" t="n">
-        <v>-9e-08</v>
+        <v>0.013494</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -9180,20 +8892,22 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Loss Per Class B Proportionate Voting Shares - Basic and Diluted $ (0.25) $ (0.31) $</t>
+          <t>Research and development 1,518,954 -</t>
         </is>
       </c>
       <c r="D165" t="inlineStr"/>
-      <c r="E165" s="5" t="n">
-        <v>-3.7e-07</v>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F165" s="5" t="n">
-        <v>-5.6e-07</v>
+        <v>2.816176</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -9214,20 +8928,22 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Class A Subordinate</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Voting Shares - Basic and Diluted 47,613,549 25,057,818</t>
+          <t>Share based payments 8, 10 491,659 -</t>
         </is>
       </c>
       <c r="D166" t="inlineStr"/>
-      <c r="E166" s="5" t="n">
-        <v>17.570051</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F166" s="5" t="n">
-        <v>44.037762</v>
+        <v>1.5549</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -9248,27 +8964,407 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Weighted Average Number of Class B Proportionate</t>
+          <t>EXPENSES</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Voting Shares - Basic and Diluted 10,000,000 10,000,000</t>
+          <t>Travel and meals 149,800 39,676</t>
         </is>
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" s="5" t="n">
+        <v>0.046165</v>
+      </c>
+      <c r="F167" s="5" t="n">
+        <v>0.495907</v>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Interest expense 7, 10 (9,351) (81,981)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" s="5" t="n">
+        <v>-0.131852</v>
+      </c>
+      <c r="F168" s="5" t="n">
+        <v>-0.015739</v>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Other income 18 3,288 118,378</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E169" s="5" t="n">
+        <v>0.496115</v>
+      </c>
+      <c r="F169" s="5" t="n">
+        <v>0.01699</v>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Grant income 3 92,031 166,976</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>0.328743</v>
+      </c>
+      <c r="F170" s="5" t="n">
+        <v>0.163598</v>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Listing expense 24 - (5,352,659)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" s="5" t="n">
+        <v>-5.352659</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>NET LOSS (4,350,363) (4,297,755)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" s="5" t="n">
+        <v>-4.784801</v>
+      </c>
+      <c r="F172" s="5" t="n">
+        <v>-9.53759</v>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Foreign exchange difference (510,196) (10,386)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" s="5" t="n">
+        <v>-0.010386</v>
+      </c>
+      <c r="F173" s="5" t="n">
+        <v>-0.511057</v>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>NET COMPREHENSIVE LOSS $ (4,860,559) $ (4,308,141) $</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" s="5" t="n">
+        <v>-4.795187</v>
+      </c>
+      <c r="F174" s="5" t="n">
+        <v>-10.048647</v>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Loss Per Class A Subordinate Voting Shares - Basic and Diluted $ (0.04) $ (0.05) $</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="F175" s="5" t="n">
+        <v>-9e-08</v>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Loss Per Class B Proportionate Voting Shares - Basic and Diluted $ (0.25) $ (0.31) $</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" s="5" t="n">
+        <v>-3.7e-07</v>
+      </c>
+      <c r="F176" s="5" t="n">
+        <v>-5.6e-07</v>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Class A Subordinate</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Voting Shares - Basic and Diluted 47,613,549 25,057,818</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" s="5" t="n">
+        <v>17.570051</v>
+      </c>
+      <c r="F177" s="5" t="n">
+        <v>44.037762</v>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Weighted Average Number of Class B Proportionate</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Voting Shares - Basic and Diluted 10,000,000 10,000,000</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="F167" s="5" t="n">
+      <c r="F178" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
         <is>
           <t>-</t>
         </is>
